--- a/data/trans_bre/P16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,16</t>
+          <t>-4,1; 2,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,52</t>
+          <t>2,4; 9,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,06</t>
+          <t>-0,23; 4,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,12</t>
+          <t>0,44; 4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 53,28</t>
+          <t>-55,79; 58,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,15; 1241,63</t>
+          <t>75,02; 1473,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 829,57</t>
+          <t>-32,36; 717,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 345,39</t>
+          <t>3,61; 327,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,27</t>
+          <t>0,69; 5,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,92</t>
+          <t>2,82; 10,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,95</t>
+          <t>0,64; 6,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,71</t>
+          <t>0,47; 3,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1636,66</t>
+          <t>-21,45; 1576,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,3; 1818,61</t>
+          <t>64,29; 1970,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 703,38</t>
+          <t>5,27; 812,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 506,5</t>
+          <t>4,21; 546,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,78</t>
+          <t>1,4; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,72</t>
+          <t>-0,24; 5,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,23</t>
+          <t>1,63; 9,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,5</t>
+          <t>4,02; 12,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,78; 601,68</t>
+          <t>28,09; 540,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 510,77</t>
+          <t>-18,74; 523,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,35; 1943,11</t>
+          <t>64,77; 2443,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130,49; 1783,0</t>
+          <t>129,68; 1562,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,62</t>
+          <t>1,32; 4,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,09</t>
+          <t>3,19; 6,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,14</t>
+          <t>0,96; 4,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,9</t>
+          <t>-0,73; 2,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,51; 403,6</t>
+          <t>54,51; 449,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>182,99; 951,85</t>
+          <t>185,89; 1051,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 366,59</t>
+          <t>36,94; 334,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 146,13</t>
+          <t>-24,21; 156,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,62</t>
+          <t>-1,19; 3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,6</t>
+          <t>3,52; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,54</t>
+          <t>1,26; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,47</t>
+          <t>0,62; 4,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 298,94</t>
+          <t>-32,63; 361,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>150,27; 1142,38</t>
+          <t>132,49; 1168,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,44; 700,97</t>
+          <t>57,57; 803,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 240,48</t>
+          <t>14,64; 251,8</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,18</t>
+          <t>4,94; 8,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,78</t>
+          <t>1,92; 5,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,57</t>
+          <t>2,69; 5,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,58</t>
+          <t>2,4; 6,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64,99; 1492,73</t>
+          <t>54,76; 1473,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,01</t>
+          <t>2,26; 4,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,52</t>
+          <t>3,74; 5,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,8</t>
+          <t>2,11; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,74</t>
+          <t>1,8; 3,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,24; 217,53</t>
+          <t>80,78; 214,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>201,3; 525,76</t>
+          <t>218,38; 534,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>126,35; 355,75</t>
+          <t>131,22; 365,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,14; 231,16</t>
+          <t>74,92; 227,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>110,74%</t>
+          <t>123,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,5</t>
+          <t>-4,62; 1,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,01</t>
+          <t>2,4; 9,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,15</t>
+          <t>0,04; 4,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,7</t>
+          <t>0,62; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 58,58</t>
+          <t>-60,6; 47,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,02; 1473,31</t>
+          <t>66,87; 1335,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 717,62</t>
+          <t>-22,07; 771,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 327,3</t>
+          <t>14,29; 386,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>150,22%</t>
+          <t>131,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,26</t>
+          <t>0,69; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,13</t>
+          <t>2,72; 9,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,06</t>
+          <t>0,53; 5,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,75</t>
+          <t>0,28; 3,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 1576,98</t>
+          <t>-25,8; 1563,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,29; 1970,93</t>
+          <t>41,81; 1800,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 812,82</t>
+          <t>4,9; 766,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 546,33</t>
+          <t>-8,73; 405,3</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>428,42%</t>
+          <t>243,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,44</t>
+          <t>1,64; 10,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,65</t>
+          <t>-0,18; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,36</t>
+          <t>1,48; 9,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,16</t>
+          <t>3,37; 11,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,09; 540,89</t>
+          <t>32,19; 528,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 523,76</t>
+          <t>-14,87; 526,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,77; 2443,99</t>
+          <t>51,02; 2072,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>129,68; 1562,08</t>
+          <t>76,38; 568,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,81</t>
+          <t>1,33; 4,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,95</t>
+          <t>3,22; 7,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,13</t>
+          <t>0,89; 4,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,99</t>
+          <t>0,71; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,51; 449,64</t>
+          <t>65,98; 442,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>185,89; 1051,27</t>
+          <t>179,48; 1048,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,94; 334,69</t>
+          <t>30,89; 361,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 156,1</t>
+          <t>20,27; 189,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>144,31%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,4</t>
+          <t>-0,98; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,63</t>
+          <t>3,52; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,61</t>
+          <t>1,24; 4,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,56</t>
+          <t>1,95; 5,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 361,33</t>
+          <t>-32,52; 297,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>132,49; 1168,94</t>
+          <t>141,61; 1184,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,57; 803,48</t>
+          <t>45,55; 702,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 251,8</t>
+          <t>51,06; 323,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>637,95%</t>
+          <t>621,42%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,07</t>
+          <t>5,08; 8,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,66</t>
+          <t>1,77; 5,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,54</t>
+          <t>2,65; 5,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,6</t>
+          <t>1,97; 5,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,76; 1473,1</t>
+          <t>44,01; 1603,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>139,29%</t>
+          <t>134,4%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,13</t>
+          <t>2,15; 3,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,62</t>
+          <t>3,73; 5,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,66</t>
+          <t>2,2; 3,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,73</t>
+          <t>2,25; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,78; 214,12</t>
+          <t>81,03; 219,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>218,38; 534,09</t>
+          <t>223,18; 535,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>131,22; 365,3</t>
+          <t>141,35; 362,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74,92; 227,38</t>
+          <t>85,08; 206,36</t>
         </is>
       </c>
     </row>
